--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_10-01-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_10-01-2026.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+          <t>£14.55</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>£19.19</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>£19.95</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>£32.15</t>
+          <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/celotex-xr4000-insulation-pitched-roof-board-1200-x-2400mm?variant=55597620494720 (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>£52.32</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-pl4050-63mm/ (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>£39.38</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>£42.70</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>£42.70</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
